--- a/streamlit_dashboard_monitoring/captured_data/with_ASCON/ppg_sensor_ascon_19.xlsx
+++ b/streamlit_dashboard_monitoring/captured_data/with_ASCON/ppg_sensor_ascon_19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:M150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,2165 +469,6735 @@
           <t>Sensor_Status</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>CPU_Load_%</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Memory_Used_%</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Latency_ms</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Enc_Time_us</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Dec_Time_ms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:53.616</t>
+          <t>2026-05-29 09:43:15.727</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1779422095436</v>
+        <v>1780022594785</v>
       </c>
       <c r="C2" t="n">
-        <v>87894</v>
+        <v>82598</v>
       </c>
       <c r="D2" t="n">
-        <v>1084.85</v>
+        <v>-16.52</v>
       </c>
       <c r="E2" t="n">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="F2" t="n">
-        <v>685</v>
+        <v>1299</v>
       </c>
       <c r="G2" t="n">
-        <v>263.68</v>
+        <v>297.05</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I2" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J2" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K2" t="n">
+        <v>941</v>
+      </c>
+      <c r="L2" t="n">
+        <v>110</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.016</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:54.171</t>
+          <t>2026-05-29 09:43:15.942</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1779422095638</v>
+        <v>1780022594985</v>
       </c>
       <c r="C3" t="n">
-        <v>88657</v>
+        <v>83076</v>
       </c>
       <c r="D3" t="n">
-        <v>1793.6</v>
+        <v>462.3</v>
       </c>
       <c r="E3" t="n">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="F3" t="n">
-        <v>705</v>
+        <v>1299</v>
       </c>
       <c r="G3" t="n">
-        <v>264.97</v>
+        <v>297.05</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I3" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J3" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K3" t="n">
+        <v>956</v>
+      </c>
+      <c r="L3" t="n">
+        <v>114</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.54</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:54.171</t>
+          <t>2026-05-29 09:43:15.968</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1779422095839</v>
+        <v>1780022595185</v>
       </c>
       <c r="C4" t="n">
-        <v>87857</v>
+        <v>83514</v>
       </c>
       <c r="D4" t="n">
-        <v>903.92</v>
+        <v>877.1900000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="F4" t="n">
-        <v>705</v>
+        <v>1299</v>
       </c>
       <c r="G4" t="n">
-        <v>264.97</v>
+        <v>297.05</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I4" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J4" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K4" t="n">
+        <v>783</v>
+      </c>
+      <c r="L4" t="n">
+        <v>107</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.749</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:54.187</t>
+          <t>2026-05-29 09:43:16.356</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1779422096041</v>
+        <v>1780022595385</v>
       </c>
       <c r="C5" t="n">
-        <v>88410</v>
+        <v>82767</v>
       </c>
       <c r="D5" t="n">
-        <v>1411.73</v>
+        <v>86.33</v>
       </c>
       <c r="E5" t="n">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="F5" t="n">
-        <v>705</v>
+        <v>1299</v>
       </c>
       <c r="G5" t="n">
-        <v>264.97</v>
+        <v>297.05</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I5" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J5" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K5" t="n">
+        <v>969</v>
+      </c>
+      <c r="L5" t="n">
+        <v>115</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.447</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:54.188</t>
+          <t>2026-05-29 09:43:16.358</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1779422096242</v>
+        <v>1780022595604</v>
       </c>
       <c r="C6" t="n">
-        <v>88832</v>
+        <v>82079</v>
       </c>
       <c r="D6" t="n">
-        <v>1763.14</v>
+        <v>-605.99</v>
       </c>
       <c r="E6" t="n">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="F6" t="n">
-        <v>584</v>
+        <v>1299</v>
       </c>
       <c r="G6" t="n">
-        <v>272.15</v>
+        <v>297.05</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I6" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J6" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K6" t="n">
+        <v>752</v>
+      </c>
+      <c r="L6" t="n">
+        <v>111</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.385</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:54.566</t>
+          <t>2026-05-29 09:43:16.920</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1779422096444</v>
+        <v>1780022595804</v>
       </c>
       <c r="C7" t="n">
-        <v>87906</v>
+        <v>82685</v>
       </c>
       <c r="D7" t="n">
-        <v>748.98</v>
+        <v>30.31</v>
       </c>
       <c r="E7" t="n">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="F7" t="n">
-        <v>584</v>
+        <v>1299</v>
       </c>
       <c r="G7" t="n">
-        <v>272.15</v>
+        <v>297.05</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I7" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J7" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1114</v>
+      </c>
+      <c r="L7" t="n">
+        <v>114</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.464</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:54.566</t>
+          <t>2026-05-29 09:43:16.922</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1779422096645</v>
+        <v>1780022596004</v>
       </c>
       <c r="C8" t="n">
-        <v>87878</v>
+        <v>82339</v>
       </c>
       <c r="D8" t="n">
-        <v>683.53</v>
+        <v>-317.2</v>
       </c>
       <c r="E8" t="n">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="F8" t="n">
-        <v>584</v>
+        <v>1299</v>
       </c>
       <c r="G8" t="n">
-        <v>272.15</v>
+        <v>297.05</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I8" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J8" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K8" t="n">
+        <v>916</v>
+      </c>
+      <c r="L8" t="n">
+        <v>111</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.423</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:54.567</t>
+          <t>2026-05-29 09:43:17.689</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1779422096846</v>
+        <v>1780022596204</v>
       </c>
       <c r="C9" t="n">
-        <v>87630</v>
+        <v>82198</v>
       </c>
       <c r="D9" t="n">
-        <v>401.36</v>
+        <v>-442.34</v>
       </c>
       <c r="E9" t="n">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="F9" t="n">
-        <v>584</v>
+        <v>1299</v>
       </c>
       <c r="G9" t="n">
-        <v>272.15</v>
+        <v>297.05</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I9" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J9" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1483</v>
+      </c>
+      <c r="L9" t="n">
+        <v>113</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.61</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:55.005</t>
+          <t>2026-05-29 09:43:17.740</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1779422097048</v>
+        <v>1780022596404</v>
       </c>
       <c r="C10" t="n">
-        <v>86617</v>
+        <v>81381</v>
       </c>
       <c r="D10" t="n">
-        <v>-631.71</v>
+        <v>-1237.23</v>
       </c>
       <c r="E10" t="n">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="F10" t="n">
-        <v>584</v>
+        <v>1299</v>
       </c>
       <c r="G10" t="n">
-        <v>272.15</v>
+        <v>297.05</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I10" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J10" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1335</v>
+      </c>
+      <c r="L10" t="n">
+        <v>111</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.154</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:55.006</t>
+          <t>2026-05-29 09:43:18.122</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1779422097249</v>
+        <v>1780022596604</v>
       </c>
       <c r="C11" t="n">
-        <v>86833</v>
+        <v>81335</v>
       </c>
       <c r="D11" t="n">
-        <v>-384.12</v>
+        <v>-1221.37</v>
       </c>
       <c r="E11" t="n">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="F11" t="n">
-        <v>584</v>
+        <v>1299</v>
       </c>
       <c r="G11" t="n">
-        <v>272.15</v>
+        <v>297.05</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I11" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J11" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1517</v>
+      </c>
+      <c r="L11" t="n">
+        <v>122</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.233</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:55.421</t>
+          <t>2026-05-29 09:43:18.124</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1779422097451</v>
+        <v>1780022596804</v>
       </c>
       <c r="C12" t="n">
-        <v>86993</v>
+        <v>82678</v>
       </c>
       <c r="D12" t="n">
-        <v>-204.92</v>
+        <v>182.7</v>
       </c>
       <c r="E12" t="n">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="F12" t="n">
-        <v>584</v>
+        <v>1299</v>
       </c>
       <c r="G12" t="n">
-        <v>272.15</v>
+        <v>297.05</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I12" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J12" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1319</v>
+      </c>
+      <c r="L12" t="n">
+        <v>120</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.295</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:55.425</t>
+          <t>2026-05-29 09:43:18.161</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1779422097652</v>
+        <v>1780022597023</v>
       </c>
       <c r="C13" t="n">
-        <v>87330</v>
+        <v>83536</v>
       </c>
       <c r="D13" t="n">
-        <v>142.33</v>
+        <v>1031.57</v>
       </c>
       <c r="E13" t="n">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="F13" t="n">
-        <v>584</v>
+        <v>1299</v>
       </c>
       <c r="G13" t="n">
-        <v>272.15</v>
+        <v>297.05</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I13" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J13" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1137</v>
+      </c>
+      <c r="L13" t="n">
+        <v>112</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.88</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:56.232</t>
+          <t>2026-05-29 09:43:18.163</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1779422097853</v>
+        <v>1780022597223</v>
       </c>
       <c r="C14" t="n">
-        <v>86512</v>
+        <v>83354</v>
       </c>
       <c r="D14" t="n">
-        <v>-682.79</v>
+        <v>797.99</v>
       </c>
       <c r="E14" t="n">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="F14" t="n">
-        <v>584</v>
+        <v>1299</v>
       </c>
       <c r="G14" t="n">
-        <v>272.15</v>
+        <v>297.05</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I14" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J14" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K14" t="n">
+        <v>939</v>
+      </c>
+      <c r="L14" t="n">
+        <v>107</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.063</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:56.233</t>
+          <t>2026-05-29 09:43:18.433</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1779422098055</v>
+        <v>1780022597423</v>
       </c>
       <c r="C15" t="n">
-        <v>86807</v>
+        <v>82797</v>
       </c>
       <c r="D15" t="n">
-        <v>-353.65</v>
+        <v>201.09</v>
       </c>
       <c r="E15" t="n">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="F15" t="n">
-        <v>584</v>
+        <v>1299</v>
       </c>
       <c r="G15" t="n">
-        <v>272.15</v>
+        <v>297.05</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I15" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J15" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1009</v>
+      </c>
+      <c r="L15" t="n">
+        <v>142</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.787</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:56.233</t>
+          <t>2026-05-29 09:43:18.434</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1779422098256</v>
+        <v>1780022597623</v>
       </c>
       <c r="C16" t="n">
-        <v>87156</v>
+        <v>82713</v>
       </c>
       <c r="D16" t="n">
-        <v>13.03</v>
+        <v>107.04</v>
       </c>
       <c r="E16" t="n">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="F16" t="n">
-        <v>584</v>
+        <v>1299</v>
       </c>
       <c r="G16" t="n">
-        <v>272.15</v>
+        <v>297.05</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I16" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J16" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K16" t="n">
+        <v>810</v>
+      </c>
+      <c r="L16" t="n">
+        <v>118</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.95</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:56.234</t>
+          <t>2026-05-29 09:43:18.870</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1779422098458</v>
+        <v>1780022597823</v>
       </c>
       <c r="C17" t="n">
-        <v>86660</v>
+        <v>82548</v>
       </c>
       <c r="D17" t="n">
-        <v>-483.62</v>
+        <v>-63.32</v>
       </c>
       <c r="E17" t="n">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="F17" t="n">
-        <v>2236</v>
+        <v>1299</v>
       </c>
       <c r="G17" t="n">
-        <v>272.15</v>
+        <v>297.05</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I17" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J17" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1045</v>
+      </c>
+      <c r="L17" t="n">
+        <v>119</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.425</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:56.621</t>
+          <t>2026-05-29 09:43:18.872</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1779422098659</v>
+        <v>1780022598023</v>
       </c>
       <c r="C18" t="n">
-        <v>86968</v>
+        <v>82527</v>
       </c>
       <c r="D18" t="n">
-        <v>-151.44</v>
+        <v>-81.15000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="F18" t="n">
-        <v>2236</v>
+        <v>1299</v>
       </c>
       <c r="G18" t="n">
-        <v>272.15</v>
+        <v>297.05</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I18" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J18" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K18" t="n">
+        <v>847</v>
+      </c>
+      <c r="L18" t="n">
+        <v>106</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.434</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:56.629</t>
+          <t>2026-05-29 09:43:19.292</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1779422098861</v>
+        <v>1780022598223</v>
       </c>
       <c r="C19" t="n">
-        <v>87200</v>
+        <v>82665</v>
       </c>
       <c r="D19" t="n">
-        <v>88.13</v>
+        <v>60.91</v>
       </c>
       <c r="E19" t="n">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="F19" t="n">
-        <v>2236</v>
+        <v>1299</v>
       </c>
       <c r="G19" t="n">
-        <v>272.15</v>
+        <v>297.05</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I19" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J19" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1068</v>
+      </c>
+      <c r="L19" t="n">
+        <v>117</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.614</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:57.051</t>
+          <t>2026-05-29 09:43:19.294</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1779422099062</v>
+        <v>1780022598423</v>
       </c>
       <c r="C20" t="n">
-        <v>87137</v>
+        <v>83091</v>
       </c>
       <c r="D20" t="n">
-        <v>20.73</v>
+        <v>483.86</v>
       </c>
       <c r="E20" t="n">
-        <v>94</v>
+        <v>52</v>
       </c>
       <c r="F20" t="n">
-        <v>584</v>
+        <v>1299</v>
       </c>
       <c r="G20" t="n">
-        <v>274.67</v>
+        <v>297.05</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I20" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J20" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K20" t="n">
+        <v>870</v>
+      </c>
+      <c r="L20" t="n">
+        <v>111</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.128</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:57.057</t>
+          <t>2026-05-29 09:43:19.836</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1779422099263</v>
+        <v>1780022598642</v>
       </c>
       <c r="C21" t="n">
-        <v>86370</v>
+        <v>83056</v>
       </c>
       <c r="D21" t="n">
-        <v>-747.3099999999999</v>
+        <v>424.67</v>
       </c>
       <c r="E21" t="n">
-        <v>94</v>
+        <v>52</v>
       </c>
       <c r="F21" t="n">
-        <v>584</v>
+        <v>1299</v>
       </c>
       <c r="G21" t="n">
-        <v>274.67</v>
+        <v>297.05</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I21" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J21" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1193</v>
+      </c>
+      <c r="L21" t="n">
+        <v>118</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.576</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:57.848</t>
+          <t>2026-05-29 09:43:19.839</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1779422099465</v>
+        <v>1780022598842</v>
       </c>
       <c r="C22" t="n">
-        <v>86615</v>
+        <v>82619</v>
       </c>
       <c r="D22" t="n">
-        <v>-464.94</v>
+        <v>-33.57</v>
       </c>
       <c r="E22" t="n">
-        <v>94</v>
+        <v>52</v>
       </c>
       <c r="F22" t="n">
-        <v>584</v>
+        <v>1299</v>
       </c>
       <c r="G22" t="n">
-        <v>274.67</v>
+        <v>297.05</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I22" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J22" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K22" t="n">
+        <v>995</v>
+      </c>
+      <c r="L22" t="n">
+        <v>110</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.954</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:57.850</t>
+          <t>2026-05-29 09:43:21.551</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1779422099666</v>
+        <v>1780022599042</v>
       </c>
       <c r="C23" t="n">
-        <v>86978</v>
+        <v>82473</v>
       </c>
       <c r="D23" t="n">
-        <v>-78.7</v>
+        <v>-177.89</v>
       </c>
       <c r="E23" t="n">
-        <v>94</v>
+        <v>52</v>
       </c>
       <c r="F23" t="n">
-        <v>584</v>
+        <v>1299</v>
       </c>
       <c r="G23" t="n">
-        <v>274.67</v>
+        <v>297.05</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I23" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J23" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2508</v>
+      </c>
+      <c r="L23" t="n">
+        <v>119</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.002</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:57.850</t>
+          <t>2026-05-29 09:43:21.553</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1779422099868</v>
+        <v>1780022599242</v>
       </c>
       <c r="C24" t="n">
-        <v>86286</v>
+        <v>83760</v>
       </c>
       <c r="D24" t="n">
-        <v>-766.76</v>
+        <v>1118.01</v>
       </c>
       <c r="E24" t="n">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="F24" t="n">
-        <v>846</v>
+        <v>1299</v>
       </c>
       <c r="G24" t="n">
-        <v>275.75</v>
+        <v>297.05</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I24" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J24" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2309</v>
+      </c>
+      <c r="L24" t="n">
+        <v>111</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.237</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:57.851</t>
+          <t>2026-05-29 09:43:21.554</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1779422100069</v>
+        <v>1780022599442</v>
       </c>
       <c r="C25" t="n">
-        <v>86653</v>
+        <v>84027</v>
       </c>
       <c r="D25" t="n">
-        <v>-361.42</v>
+        <v>1329.11</v>
       </c>
       <c r="E25" t="n">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="F25" t="n">
-        <v>846</v>
+        <v>6196</v>
       </c>
       <c r="G25" t="n">
-        <v>275.75</v>
+        <v>297.05</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I25" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J25" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2111</v>
+      </c>
+      <c r="L25" t="n">
+        <v>111</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.285</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:58.254</t>
+          <t>2026-05-29 09:43:21.555</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1779422100270</v>
+        <v>1780022599642</v>
       </c>
       <c r="C26" t="n">
-        <v>86805</v>
+        <v>83973</v>
       </c>
       <c r="D26" t="n">
-        <v>-191.35</v>
+        <v>1208.65</v>
       </c>
       <c r="E26" t="n">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="F26" t="n">
-        <v>846</v>
+        <v>6196</v>
       </c>
       <c r="G26" t="n">
-        <v>275.75</v>
+        <v>297.05</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I26" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J26" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1912</v>
+      </c>
+      <c r="L26" t="n">
+        <v>123</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.96</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:58.255</t>
+          <t>2026-05-29 09:43:22.163</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1779422100472</v>
+        <v>1780022599842</v>
       </c>
       <c r="C27" t="n">
-        <v>87108</v>
+        <v>83782</v>
       </c>
       <c r="D27" t="n">
-        <v>121.22</v>
+        <v>957.22</v>
       </c>
       <c r="E27" t="n">
-        <v>93</v>
+        <v>52</v>
       </c>
       <c r="F27" t="n">
-        <v>604</v>
+        <v>6196</v>
       </c>
       <c r="G27" t="n">
-        <v>279.6</v>
+        <v>297.05</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I27" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J27" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2321</v>
+      </c>
+      <c r="L27" t="n">
+        <v>107</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.515</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:58.947</t>
+          <t>2026-05-29 09:43:22.165</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1779422100673</v>
+        <v>1780022600042</v>
       </c>
       <c r="C28" t="n">
-        <v>86321</v>
+        <v>82383</v>
       </c>
       <c r="D28" t="n">
-        <v>-671.85</v>
+        <v>-489.64</v>
       </c>
       <c r="E28" t="n">
-        <v>93</v>
+        <v>52</v>
       </c>
       <c r="F28" t="n">
-        <v>604</v>
+        <v>6196</v>
       </c>
       <c r="G28" t="n">
-        <v>279.6</v>
+        <v>297.05</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I28" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J28" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2122</v>
+      </c>
+      <c r="L28" t="n">
+        <v>113</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.08</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:58.948</t>
+          <t>2026-05-29 09:43:22.166</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1779422100875</v>
+        <v>1780022600261</v>
       </c>
       <c r="C29" t="n">
-        <v>86594</v>
+        <v>82479</v>
       </c>
       <c r="D29" t="n">
-        <v>-365.25</v>
+        <v>-369.16</v>
       </c>
       <c r="E29" t="n">
-        <v>93</v>
+        <v>52</v>
       </c>
       <c r="F29" t="n">
-        <v>604</v>
+        <v>6196</v>
       </c>
       <c r="G29" t="n">
-        <v>279.6</v>
+        <v>297.05</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I29" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J29" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1904</v>
+      </c>
+      <c r="L29" t="n">
+        <v>122</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.641</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:58.949</t>
+          <t>2026-05-29 09:43:22.167</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1779422101076</v>
+        <v>1780022600461</v>
       </c>
       <c r="C30" t="n">
-        <v>86938</v>
+        <v>82829</v>
       </c>
       <c r="D30" t="n">
-        <v>-2.99</v>
+        <v>-0.7</v>
       </c>
       <c r="E30" t="n">
-        <v>93</v>
+        <v>52</v>
       </c>
       <c r="F30" t="n">
-        <v>604</v>
+        <v>6196</v>
       </c>
       <c r="G30" t="n">
-        <v>279.6</v>
+        <v>297.05</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I30" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J30" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1705</v>
+      </c>
+      <c r="L30" t="n">
+        <v>106</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.522</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:59.299</t>
+          <t>2026-05-29 09:43:22.173</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1779422101277</v>
+        <v>1780022600661</v>
       </c>
       <c r="C31" t="n">
-        <v>86631</v>
+        <v>82667</v>
       </c>
       <c r="D31" t="n">
-        <v>-309.84</v>
+        <v>-162.67</v>
       </c>
       <c r="E31" t="n">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="F31" t="n">
-        <v>765</v>
+        <v>6196</v>
       </c>
       <c r="G31" t="n">
-        <v>276.64</v>
+        <v>297.05</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I31" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J31" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1511</v>
+      </c>
+      <c r="L31" t="n">
+        <v>113</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.571</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:59.301</t>
+          <t>2026-05-29 09:43:22.288</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1779422101479</v>
+        <v>1780022600861</v>
       </c>
       <c r="C32" t="n">
-        <v>86731</v>
+        <v>82210</v>
       </c>
       <c r="D32" t="n">
-        <v>-194.35</v>
+        <v>-611.53</v>
       </c>
       <c r="E32" t="n">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="F32" t="n">
-        <v>765</v>
+        <v>6196</v>
       </c>
       <c r="G32" t="n">
-        <v>276.64</v>
+        <v>297.05</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I32" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J32" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1426</v>
+      </c>
+      <c r="L32" t="n">
+        <v>123</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.028</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:59.758</t>
+          <t>2026-05-29 09:43:22.289</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1779422101680</v>
+        <v>1780022601061</v>
       </c>
       <c r="C33" t="n">
-        <v>86858</v>
+        <v>82139</v>
       </c>
       <c r="D33" t="n">
-        <v>-57.63</v>
+        <v>-651.96</v>
       </c>
       <c r="E33" t="n">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="F33" t="n">
-        <v>765</v>
+        <v>6196</v>
       </c>
       <c r="G33" t="n">
-        <v>276.64</v>
+        <v>297.05</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I33" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J33" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1228</v>
+      </c>
+      <c r="L33" t="n">
+        <v>113</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.517</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:59.759</t>
+          <t>2026-05-29 09:43:22.290</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1779422101882</v>
+        <v>1780022601261</v>
       </c>
       <c r="C34" t="n">
-        <v>87080</v>
+        <v>82320</v>
       </c>
       <c r="D34" t="n">
-        <v>167.25</v>
+        <v>-438.36</v>
       </c>
       <c r="E34" t="n">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="F34" t="n">
-        <v>665</v>
+        <v>6196</v>
       </c>
       <c r="G34" t="n">
-        <v>249.58</v>
+        <v>297.05</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I34" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J34" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1028</v>
+      </c>
+      <c r="L34" t="n">
+        <v>105</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.499</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-22 10:55:00.140</t>
+          <t>2026-05-29 09:43:22.588</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1779422102083</v>
+        <v>1780022601461</v>
       </c>
       <c r="C35" t="n">
-        <v>86551</v>
+        <v>82239</v>
       </c>
       <c r="D35" t="n">
-        <v>-370.11</v>
+        <v>-497.44</v>
       </c>
       <c r="E35" t="n">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="F35" t="n">
-        <v>665</v>
+        <v>6196</v>
       </c>
       <c r="G35" t="n">
-        <v>249.58</v>
+        <v>297.05</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I35" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J35" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1126</v>
+      </c>
+      <c r="L35" t="n">
+        <v>125</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.9419999999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-22 10:55:00.141</t>
+          <t>2026-05-29 09:43:22.607</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1779422102284</v>
+        <v>1780022601661</v>
       </c>
       <c r="C36" t="n">
-        <v>86872</v>
+        <v>82398</v>
       </c>
       <c r="D36" t="n">
-        <v>-30.61</v>
+        <v>-313.57</v>
       </c>
       <c r="E36" t="n">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="F36" t="n">
-        <v>665</v>
+        <v>6196</v>
       </c>
       <c r="G36" t="n">
-        <v>249.58</v>
+        <v>297.05</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I36" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J36" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K36" t="n">
+        <v>945</v>
+      </c>
+      <c r="L36" t="n">
+        <v>111</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.033</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-22 10:55:00.526</t>
+          <t>2026-05-29 09:43:23.142</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1779422102486</v>
+        <v>1780022601880</v>
       </c>
       <c r="C37" t="n">
-        <v>87138</v>
+        <v>82441</v>
       </c>
       <c r="D37" t="n">
-        <v>236.92</v>
+        <v>-254.89</v>
       </c>
       <c r="E37" t="n">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="F37" t="n">
-        <v>644</v>
+        <v>2558</v>
       </c>
       <c r="G37" t="n">
-        <v>89.28</v>
+        <v>297.05</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I37" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J37" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1259</v>
+      </c>
+      <c r="L37" t="n">
+        <v>122</v>
+      </c>
+      <c r="M37" t="n">
+        <v>2.33</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-22 10:55:00.527</t>
+          <t>2026-05-29 09:43:23.145</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1779422102687</v>
+        <v>1780022602080</v>
       </c>
       <c r="C38" t="n">
-        <v>86344</v>
+        <v>82113</v>
       </c>
       <c r="D38" t="n">
-        <v>-568.92</v>
+        <v>-570.15</v>
       </c>
       <c r="E38" t="n">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="F38" t="n">
-        <v>644</v>
+        <v>2558</v>
       </c>
       <c r="G38" t="n">
-        <v>89.28</v>
+        <v>297.05</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I38" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J38" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1063</v>
+      </c>
+      <c r="L38" t="n">
+        <v>106</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.613</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-22 10:55:00.920</t>
+          <t>2026-05-29 09:43:23.755</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1779422102889</v>
+        <v>1780022602281</v>
       </c>
       <c r="C39" t="n">
-        <v>86498</v>
+        <v>81805</v>
       </c>
       <c r="D39" t="n">
-        <v>-386.48</v>
+        <v>-849.64</v>
       </c>
       <c r="E39" t="n">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="F39" t="n">
-        <v>644</v>
+        <v>2558</v>
       </c>
       <c r="G39" t="n">
-        <v>89.28</v>
+        <v>297.05</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I39" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J39" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1473</v>
+      </c>
+      <c r="L39" t="n">
+        <v>108</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.374</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-22 10:55:00.921</t>
+          <t>2026-05-29 09:43:23.757</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1779422103090</v>
+        <v>1780022602480</v>
       </c>
       <c r="C40" t="n">
-        <v>86296</v>
+        <v>82177</v>
       </c>
       <c r="D40" t="n">
-        <v>-569.15</v>
+        <v>-435.16</v>
       </c>
       <c r="E40" t="n">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="F40" t="n">
-        <v>644</v>
+        <v>2558</v>
       </c>
       <c r="G40" t="n">
-        <v>89.28</v>
+        <v>297.05</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I40" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J40" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1276</v>
+      </c>
+      <c r="L40" t="n">
+        <v>105</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.015</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-22 10:55:01.441</t>
+          <t>2026-05-29 09:43:23.759</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1779422103292</v>
+        <v>1780022602680</v>
       </c>
       <c r="C41" t="n">
-        <v>86574</v>
+        <v>81786</v>
       </c>
       <c r="D41" t="n">
-        <v>-262.7</v>
+        <v>-804.4</v>
       </c>
       <c r="E41" t="n">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="F41" t="n">
-        <v>644</v>
+        <v>820</v>
       </c>
       <c r="G41" t="n">
-        <v>89.28</v>
+        <v>303.83</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I41" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J41" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1078</v>
+      </c>
+      <c r="L41" t="n">
+        <v>106</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.991</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-22 10:55:01.442</t>
+          <t>2026-05-29 09:43:24.274</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1779422103493</v>
+        <v>1780022602880</v>
       </c>
       <c r="C42" t="n">
-        <v>85603</v>
+        <v>82469</v>
       </c>
       <c r="D42" t="n">
-        <v>-1220.56</v>
+        <v>-81.18000000000001</v>
       </c>
       <c r="E42" t="n">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="F42" t="n">
-        <v>644</v>
+        <v>820</v>
       </c>
       <c r="G42" t="n">
-        <v>89.28</v>
+        <v>303.83</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I42" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J42" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1392</v>
+      </c>
+      <c r="L42" t="n">
+        <v>111</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.285</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-22 10:55:01.442</t>
+          <t>2026-05-29 09:43:24.275</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1779422103694</v>
+        <v>1780022603080</v>
       </c>
       <c r="C43" t="n">
-        <v>85811</v>
+        <v>82226</v>
       </c>
       <c r="D43" t="n">
-        <v>-951.53</v>
+        <v>-320.12</v>
       </c>
       <c r="E43" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="F43" t="n">
-        <v>644</v>
+        <v>340</v>
       </c>
       <c r="G43" t="n">
-        <v>89.28</v>
+        <v>336.02</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I43" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J43" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1194</v>
+      </c>
+      <c r="L43" t="n">
+        <v>106</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.042</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05-22 10:55:01.757</t>
+          <t>2026-05-29 09:43:24.277</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1779422103896</v>
+        <v>1780022603280</v>
       </c>
       <c r="C44" t="n">
-        <v>86173</v>
+        <v>82119</v>
       </c>
       <c r="D44" t="n">
-        <v>-541.96</v>
+        <v>-411.11</v>
       </c>
       <c r="E44" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="F44" t="n">
-        <v>644</v>
+        <v>340</v>
       </c>
       <c r="G44" t="n">
-        <v>89.28</v>
+        <v>336.02</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I44" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J44" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K44" t="n">
+        <v>996</v>
+      </c>
+      <c r="L44" t="n">
+        <v>104</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.753</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-22 10:55:02.163</t>
+          <t>2026-05-29 09:43:24.725</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1779422104097</v>
+        <v>1780022603499</v>
       </c>
       <c r="C45" t="n">
-        <v>85666</v>
+        <v>82080</v>
       </c>
       <c r="D45" t="n">
-        <v>-1021.86</v>
+        <v>-429.56</v>
       </c>
       <c r="E45" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="F45" t="n">
-        <v>1612</v>
+        <v>340</v>
       </c>
       <c r="G45" t="n">
-        <v>89.28</v>
+        <v>336.02</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I45" t="n">
+        <v>49.47</v>
+      </c>
+      <c r="J45" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1225</v>
+      </c>
+      <c r="L45" t="n">
+        <v>116</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1.378</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-05-22 10:55:02.164</t>
+          <t>2026-05-29 09:43:24.787</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1779422104299</v>
+        <v>1780022603699</v>
       </c>
       <c r="C46" t="n">
-        <v>85815</v>
+        <v>82299</v>
       </c>
       <c r="D46" t="n">
-        <v>-821.76</v>
+        <v>-189.08</v>
       </c>
       <c r="E46" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="F46" t="n">
-        <v>1612</v>
+        <v>340</v>
       </c>
       <c r="G46" t="n">
-        <v>89.28</v>
+        <v>336.02</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I46" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J46" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1088</v>
+      </c>
+      <c r="L46" t="n">
+        <v>106</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.639</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-22 10:55:02.560</t>
+          <t>2026-05-29 09:43:25.160</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1779422104500</v>
+        <v>1780022603899</v>
       </c>
       <c r="C47" t="n">
-        <v>85962</v>
+        <v>82367</v>
       </c>
       <c r="D47" t="n">
-        <v>-633.6799999999999</v>
+        <v>-111.63</v>
       </c>
       <c r="E47" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F47" t="n">
-        <v>1612</v>
+        <v>799</v>
       </c>
       <c r="G47" t="n">
-        <v>89.28</v>
+        <v>319.5</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I47" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J47" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1260</v>
+      </c>
+      <c r="L47" t="n">
+        <v>114</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1.404</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-05-22 10:55:02.561</t>
+          <t>2026-05-29 09:43:25.163</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1779422104701</v>
+        <v>1780022604099</v>
       </c>
       <c r="C48" t="n">
-        <v>86208</v>
+        <v>82367</v>
       </c>
       <c r="D48" t="n">
-        <v>-355.99</v>
+        <v>-106.04</v>
       </c>
       <c r="E48" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F48" t="n">
-        <v>604</v>
+        <v>799</v>
       </c>
       <c r="G48" t="n">
-        <v>85.40000000000001</v>
+        <v>319.5</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I48" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J48" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1062</v>
+      </c>
+      <c r="L48" t="n">
+        <v>112</v>
+      </c>
+      <c r="M48" t="n">
+        <v>2.186</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-22 10:55:03.003</t>
+          <t>2026-05-29 09:43:25.842</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1779422104903</v>
+        <v>1780022604299</v>
       </c>
       <c r="C49" t="n">
-        <v>85624</v>
+        <v>82366</v>
       </c>
       <c r="D49" t="n">
-        <v>-922.1900000000001</v>
+        <v>-101.74</v>
       </c>
       <c r="E49" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F49" t="n">
-        <v>604</v>
+        <v>799</v>
       </c>
       <c r="G49" t="n">
-        <v>85.40000000000001</v>
+        <v>319.5</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I49" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J49" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1542</v>
+      </c>
+      <c r="L49" t="n">
+        <v>114</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.638</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-22 10:55:03.003</t>
+          <t>2026-05-29 09:43:25.843</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1779422105104</v>
+        <v>1780022604499</v>
       </c>
       <c r="C50" t="n">
-        <v>86044</v>
+        <v>82329</v>
       </c>
       <c r="D50" t="n">
-        <v>-456.08</v>
+        <v>-133.66</v>
       </c>
       <c r="E50" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F50" t="n">
-        <v>604</v>
+        <v>799</v>
       </c>
       <c r="G50" t="n">
-        <v>85.40000000000001</v>
+        <v>319.5</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I50" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J50" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1343</v>
+      </c>
+      <c r="L50" t="n">
+        <v>116</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.578</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-22 10:55:03.285</t>
+          <t>2026-05-29 09:43:25.844</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1779422105306</v>
+        <v>1780022604699</v>
       </c>
       <c r="C51" t="n">
-        <v>86288</v>
+        <v>82255</v>
       </c>
       <c r="D51" t="n">
-        <v>-189.28</v>
+        <v>-200.97</v>
       </c>
       <c r="E51" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F51" t="n">
-        <v>604</v>
+        <v>799</v>
       </c>
       <c r="G51" t="n">
-        <v>87.48999999999999</v>
+        <v>319.5</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I51" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J51" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1144</v>
+      </c>
+      <c r="L51" t="n">
+        <v>105</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.776</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-22 10:55:03.286</t>
+          <t>2026-05-29 09:43:26.436</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1779422105507</v>
+        <v>1780022604918</v>
       </c>
       <c r="C52" t="n">
-        <v>85698</v>
+        <v>82200</v>
       </c>
       <c r="D52" t="n">
-        <v>-769.8200000000001</v>
+        <v>-245.92</v>
       </c>
       <c r="E52" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F52" t="n">
-        <v>604</v>
+        <v>799</v>
       </c>
       <c r="G52" t="n">
-        <v>87.48999999999999</v>
+        <v>319.5</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I52" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J52" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1517</v>
+      </c>
+      <c r="L52" t="n">
+        <v>116</v>
+      </c>
+      <c r="M52" t="n">
+        <v>1.166</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-05-22 10:55:03.606</t>
+          <t>2026-05-29 09:43:26.451</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1779422105708</v>
+        <v>1780022605118</v>
       </c>
       <c r="C53" t="n">
-        <v>86103</v>
+        <v>82005</v>
       </c>
       <c r="D53" t="n">
-        <v>-326.32</v>
+        <v>-428.63</v>
       </c>
       <c r="E53" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F53" t="n">
-        <v>604</v>
+        <v>799</v>
       </c>
       <c r="G53" t="n">
-        <v>87.48999999999999</v>
+        <v>319.5</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I53" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J53" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1332</v>
+      </c>
+      <c r="L53" t="n">
+        <v>114</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1.213</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-05-22 10:55:04.003</t>
+          <t>2026-05-29 09:43:26.452</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1779422105910</v>
+        <v>1780022605318</v>
       </c>
       <c r="C54" t="n">
-        <v>86270</v>
+        <v>81878</v>
       </c>
       <c r="D54" t="n">
-        <v>-143.01</v>
+        <v>-534.2</v>
       </c>
       <c r="E54" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F54" t="n">
-        <v>665</v>
+        <v>799</v>
       </c>
       <c r="G54" t="n">
-        <v>86.13</v>
+        <v>319.5</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I54" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J54" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1134</v>
+      </c>
+      <c r="L54" t="n">
+        <v>105</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.758</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-05-22 10:55:04.004</t>
+          <t>2026-05-29 09:43:26.936</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1779422106111</v>
+        <v>1780022605518</v>
       </c>
       <c r="C55" t="n">
-        <v>86121</v>
+        <v>82193</v>
       </c>
       <c r="D55" t="n">
-        <v>-284.86</v>
+        <v>-192.49</v>
       </c>
       <c r="E55" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F55" t="n">
-        <v>665</v>
+        <v>799</v>
       </c>
       <c r="G55" t="n">
-        <v>86.13</v>
+        <v>319.5</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I55" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J55" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K55" t="n">
+        <v>1416</v>
+      </c>
+      <c r="L55" t="n">
+        <v>116</v>
+      </c>
+      <c r="M55" t="n">
+        <v>2.366</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-05-22 10:55:04.402</t>
+          <t>2026-05-29 09:43:26.939</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1779422106313</v>
+        <v>1780022605718</v>
       </c>
       <c r="C56" t="n">
-        <v>85860</v>
+        <v>82491</v>
       </c>
       <c r="D56" t="n">
-        <v>-531.62</v>
+        <v>115.14</v>
       </c>
       <c r="E56" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F56" t="n">
-        <v>665</v>
+        <v>1859</v>
       </c>
       <c r="G56" t="n">
-        <v>86.13</v>
+        <v>319.5</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I56" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J56" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K56" t="n">
+        <v>1219</v>
+      </c>
+      <c r="L56" t="n">
+        <v>118</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1.644</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-05-22 10:55:04.402</t>
+          <t>2026-05-29 09:43:26.941</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1779422106514</v>
+        <v>1780022605918</v>
       </c>
       <c r="C57" t="n">
-        <v>86091</v>
+        <v>82338</v>
       </c>
       <c r="D57" t="n">
-        <v>-274.03</v>
+        <v>-43.62</v>
       </c>
       <c r="E57" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F57" t="n">
-        <v>665</v>
+        <v>1859</v>
       </c>
       <c r="G57" t="n">
-        <v>86.13</v>
+        <v>319.5</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I57" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J57" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K57" t="n">
+        <v>1022</v>
+      </c>
+      <c r="L57" t="n">
+        <v>106</v>
+      </c>
+      <c r="M57" t="n">
+        <v>1.637</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-05-22 10:55:04.820</t>
+          <t>2026-05-29 09:43:27.606</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1779422106715</v>
+        <v>1780022606119</v>
       </c>
       <c r="C58" t="n">
-        <v>86360</v>
+        <v>82342</v>
       </c>
       <c r="D58" t="n">
-        <v>8.67</v>
+        <v>-37.44</v>
       </c>
       <c r="E58" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F58" t="n">
-        <v>785</v>
+        <v>1859</v>
       </c>
       <c r="G58" t="n">
-        <v>90.66</v>
+        <v>319.5</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I58" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="J58" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K58" t="n">
+        <v>1486</v>
+      </c>
+      <c r="L58" t="n">
+        <v>105</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1.022</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-05-22 10:55:04.833</t>
+          <t>2026-05-29 09:43:27.637</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1779422106917</v>
+        <v>1780022606318</v>
       </c>
       <c r="C59" t="n">
-        <v>85621</v>
+        <v>82327</v>
       </c>
       <c r="D59" t="n">
-        <v>-730.77</v>
+        <v>-50.57</v>
       </c>
       <c r="E59" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F59" t="n">
-        <v>785</v>
+        <v>1859</v>
       </c>
       <c r="G59" t="n">
-        <v>90.66</v>
+        <v>319.5</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I59" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J59" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K59" t="n">
+        <v>1318</v>
+      </c>
+      <c r="L59" t="n">
+        <v>109</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1.293</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-05-22 10:55:05.234</t>
+          <t>2026-05-29 09:43:28.292</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1779422107118</v>
+        <v>1780022606519</v>
       </c>
       <c r="C60" t="n">
-        <v>85789</v>
+        <v>82225</v>
       </c>
       <c r="D60" t="n">
-        <v>-526.23</v>
+        <v>-150.04</v>
       </c>
       <c r="E60" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F60" t="n">
-        <v>785</v>
+        <v>1859</v>
       </c>
       <c r="G60" t="n">
-        <v>90.66</v>
+        <v>319.5</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I60" t="n">
+        <v>49.63</v>
+      </c>
+      <c r="J60" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1772</v>
+      </c>
+      <c r="L60" t="n">
+        <v>105</v>
+      </c>
+      <c r="M60" t="n">
+        <v>1.533</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-05-22 10:55:05.235</t>
+          <t>2026-05-29 09:43:28.314</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1779422107320</v>
+        <v>1780022606737</v>
       </c>
       <c r="C61" t="n">
-        <v>86052</v>
+        <v>82154</v>
       </c>
       <c r="D61" t="n">
-        <v>-236.92</v>
+        <v>-213.54</v>
       </c>
       <c r="E61" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F61" t="n">
-        <v>785</v>
+        <v>1859</v>
       </c>
       <c r="G61" t="n">
-        <v>90.66</v>
+        <v>319.5</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I61" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J61" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1576</v>
+      </c>
+      <c r="L61" t="n">
+        <v>117</v>
+      </c>
+      <c r="M61" t="n">
+        <v>1.264</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-05-22 10:55:05.668</t>
+          <t>2026-05-29 09:43:28.316</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1779422107521</v>
+        <v>1780022606937</v>
       </c>
       <c r="C62" t="n">
-        <v>85343</v>
+        <v>82095</v>
       </c>
       <c r="D62" t="n">
-        <v>-934.0700000000001</v>
+        <v>-261.86</v>
       </c>
       <c r="E62" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F62" t="n">
-        <v>725</v>
+        <v>1859</v>
       </c>
       <c r="G62" t="n">
-        <v>85.48</v>
+        <v>319.5</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I62" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J62" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K62" t="n">
+        <v>1377</v>
+      </c>
+      <c r="L62" t="n">
+        <v>109</v>
+      </c>
+      <c r="M62" t="n">
+        <v>1.27</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-05-22 10:55:05.694</t>
+          <t>2026-05-29 09:43:28.318</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1779422107722</v>
+        <v>1780022607137</v>
       </c>
       <c r="C63" t="n">
-        <v>85668</v>
+        <v>82165</v>
       </c>
       <c r="D63" t="n">
-        <v>-562.37</v>
+        <v>-178.77</v>
       </c>
       <c r="E63" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F63" t="n">
-        <v>725</v>
+        <v>1859</v>
       </c>
       <c r="G63" t="n">
-        <v>85.48</v>
+        <v>319.5</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I63" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J63" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K63" t="n">
+        <v>1179</v>
+      </c>
+      <c r="L63" t="n">
+        <v>108</v>
+      </c>
+      <c r="M63" t="n">
+        <v>1.449</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-05-22 10:55:06.052</t>
+          <t>2026-05-29 09:43:28.719</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1779422107924</v>
+        <v>1780022607337</v>
       </c>
       <c r="C64" t="n">
-        <v>85823</v>
+        <v>81885</v>
       </c>
       <c r="D64" t="n">
-        <v>-379.25</v>
+        <v>-449.83</v>
       </c>
       <c r="E64" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F64" t="n">
-        <v>725</v>
+        <v>1859</v>
       </c>
       <c r="G64" t="n">
-        <v>85.48</v>
+        <v>319.5</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I64" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J64" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K64" t="n">
+        <v>1381</v>
+      </c>
+      <c r="L64" t="n">
+        <v>115</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1.168</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-05-22 10:55:06.053</t>
+          <t>2026-05-29 09:43:28.721</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1779422108125</v>
+        <v>1780022607537</v>
       </c>
       <c r="C65" t="n">
-        <v>85465</v>
+        <v>81804</v>
       </c>
       <c r="D65" t="n">
-        <v>-718.29</v>
+        <v>-508.34</v>
       </c>
       <c r="E65" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F65" t="n">
-        <v>604</v>
+        <v>1859</v>
       </c>
       <c r="G65" t="n">
-        <v>69.36</v>
+        <v>319.5</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I65" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J65" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K65" t="n">
+        <v>1183</v>
+      </c>
+      <c r="L65" t="n">
+        <v>119</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0.6850000000000001</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-05-22 10:55:06.053</t>
+          <t>2026-05-29 09:43:28.732</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1779422108327</v>
+        <v>1780022607737</v>
       </c>
       <c r="C66" t="n">
-        <v>85802</v>
+        <v>82161</v>
       </c>
       <c r="D66" t="n">
-        <v>-345.37</v>
+        <v>-125.92</v>
       </c>
       <c r="E66" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F66" t="n">
-        <v>604</v>
+        <v>1859</v>
       </c>
       <c r="G66" t="n">
-        <v>69.36</v>
+        <v>319.5</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I66" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J66" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="K66" t="n">
+        <v>994</v>
+      </c>
+      <c r="L66" t="n">
+        <v>149</v>
+      </c>
+      <c r="M66" t="n">
+        <v>1.275</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-05-22 10:55:06.459</t>
+          <t>2026-05-29 09:43:28.999</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1779422108528</v>
+        <v>1780022607938</v>
       </c>
       <c r="C67" t="n">
-        <v>85858</v>
+        <v>82404</v>
       </c>
       <c r="D67" t="n">
-        <v>-272.1</v>
+        <v>123.38</v>
       </c>
       <c r="E67" t="n">
         <v>92</v>
       </c>
       <c r="F67" t="n">
-        <v>524</v>
+        <v>2279</v>
       </c>
       <c r="G67" t="n">
-        <v>81.01000000000001</v>
+        <v>319.5</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I67" t="n">
+        <v>49.44</v>
+      </c>
+      <c r="J67" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K67" t="n">
+        <v>1060</v>
+      </c>
+      <c r="L67" t="n">
+        <v>108</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.781</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-05-22 10:55:06.460</t>
+          <t>2026-05-29 09:43:29.032</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1779422108729</v>
+        <v>1780022608137</v>
       </c>
       <c r="C68" t="n">
-        <v>85921</v>
+        <v>82695</v>
       </c>
       <c r="D68" t="n">
-        <v>-195.5</v>
+        <v>408.21</v>
       </c>
       <c r="E68" t="n">
         <v>92</v>
       </c>
       <c r="F68" t="n">
-        <v>524</v>
+        <v>2279</v>
       </c>
       <c r="G68" t="n">
-        <v>81.01000000000001</v>
+        <v>319.5</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I68" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J68" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K68" t="n">
+        <v>894</v>
+      </c>
+      <c r="L68" t="n">
+        <v>98</v>
+      </c>
+      <c r="M68" t="n">
+        <v>1.015</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-05-22 10:55:06.880</t>
+          <t>2026-05-29 09:43:29.261</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1779422108931</v>
+        <v>1780022608356</v>
       </c>
       <c r="C69" t="n">
-        <v>85179</v>
+        <v>83049</v>
       </c>
       <c r="D69" t="n">
-        <v>-927.72</v>
+        <v>741.8</v>
       </c>
       <c r="E69" t="n">
         <v>92</v>
       </c>
       <c r="F69" t="n">
-        <v>524</v>
+        <v>2279</v>
       </c>
       <c r="G69" t="n">
-        <v>81.01000000000001</v>
+        <v>319.5</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I69" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J69" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K69" t="n">
+        <v>904</v>
+      </c>
+      <c r="L69" t="n">
+        <v>120</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.975</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-05-22 10:55:06.926</t>
+          <t>2026-05-29 09:43:29.342</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1779422109132</v>
+        <v>1780022608556</v>
       </c>
       <c r="C70" t="n">
-        <v>85362</v>
+        <v>82960</v>
       </c>
       <c r="D70" t="n">
-        <v>-698.34</v>
+        <v>615.71</v>
       </c>
       <c r="E70" t="n">
         <v>92</v>
       </c>
       <c r="F70" t="n">
-        <v>524</v>
+        <v>2279</v>
       </c>
       <c r="G70" t="n">
-        <v>81.01000000000001</v>
+        <v>319.5</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I70" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J70" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K70" t="n">
+        <v>785</v>
+      </c>
+      <c r="L70" t="n">
+        <v>154</v>
+      </c>
+      <c r="M70" t="n">
+        <v>1.062</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-05-22 10:55:07.265</t>
+          <t>2026-05-29 09:43:29.698</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1779422109334</v>
+        <v>1780022608757</v>
       </c>
       <c r="C71" t="n">
-        <v>85518</v>
+        <v>82815</v>
       </c>
       <c r="D71" t="n">
-        <v>-507.42</v>
+        <v>439.92</v>
       </c>
       <c r="E71" t="n">
         <v>92</v>
       </c>
       <c r="F71" t="n">
-        <v>524</v>
+        <v>2279</v>
       </c>
       <c r="G71" t="n">
-        <v>81.01000000000001</v>
+        <v>319.5</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I71" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J71" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K71" t="n">
+        <v>939</v>
+      </c>
+      <c r="L71" t="n">
+        <v>108</v>
+      </c>
+      <c r="M71" t="n">
+        <v>1.942</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-05-22 10:55:07.266</t>
+          <t>2026-05-29 09:43:29.748</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1779422109535</v>
+        <v>1780022608956</v>
       </c>
       <c r="C72" t="n">
-        <v>84851</v>
+        <v>82733</v>
       </c>
       <c r="D72" t="n">
-        <v>-1149.05</v>
+        <v>335.93</v>
       </c>
       <c r="E72" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F72" t="n">
-        <v>947</v>
+        <v>2279</v>
       </c>
       <c r="G72" t="n">
-        <v>119.09</v>
+        <v>319.5</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I72" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J72" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K72" t="n">
+        <v>791</v>
+      </c>
+      <c r="L72" t="n">
+        <v>108</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0.831</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-05-22 10:55:07.703</t>
+          <t>2026-05-29 09:43:30.287</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1779422109736</v>
+        <v>1780022609156</v>
       </c>
       <c r="C73" t="n">
-        <v>86244</v>
+        <v>83212</v>
       </c>
       <c r="D73" t="n">
-        <v>301.4</v>
+        <v>798.13</v>
       </c>
       <c r="E73" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F73" t="n">
-        <v>947</v>
+        <v>2279</v>
       </c>
       <c r="G73" t="n">
-        <v>119.09</v>
+        <v>319.5</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I73" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J73" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K73" t="n">
+        <v>1130</v>
+      </c>
+      <c r="L73" t="n">
+        <v>120</v>
+      </c>
+      <c r="M73" t="n">
+        <v>1.395</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:30.289</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>1780022609356</v>
+      </c>
+      <c r="C74" t="n">
+        <v>83247</v>
+      </c>
+      <c r="D74" t="n">
+        <v>793.22</v>
+      </c>
+      <c r="E74" t="n">
+        <v>92</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1259</v>
+      </c>
+      <c r="G74" t="n">
+        <v>309.22</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J74" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K74" t="n">
+        <v>932</v>
+      </c>
+      <c r="L74" t="n">
+        <v>117</v>
+      </c>
+      <c r="M74" t="n">
+        <v>1.447</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:30.292</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>1780022609556</v>
+      </c>
+      <c r="C75" t="n">
+        <v>83238</v>
+      </c>
+      <c r="D75" t="n">
+        <v>744.5599999999999</v>
+      </c>
+      <c r="E75" t="n">
+        <v>92</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1259</v>
+      </c>
+      <c r="G75" t="n">
+        <v>309.22</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J75" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K75" t="n">
+        <v>734</v>
+      </c>
+      <c r="L75" t="n">
+        <v>108</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.175</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:30.985</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>1780022609756</v>
+      </c>
+      <c r="C76" t="n">
+        <v>83431</v>
+      </c>
+      <c r="D76" t="n">
+        <v>900.33</v>
+      </c>
+      <c r="E76" t="n">
+        <v>92</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1259</v>
+      </c>
+      <c r="G76" t="n">
+        <v>309.22</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J76" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K76" t="n">
+        <v>1228</v>
+      </c>
+      <c r="L76" t="n">
+        <v>121</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0.905</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:30.987</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>1780022609956</v>
+      </c>
+      <c r="C77" t="n">
+        <v>82950</v>
+      </c>
+      <c r="D77" t="n">
+        <v>374.32</v>
+      </c>
+      <c r="E77" t="n">
+        <v>92</v>
+      </c>
+      <c r="F77" t="n">
+        <v>1259</v>
+      </c>
+      <c r="G77" t="n">
+        <v>309.22</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J77" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K77" t="n">
+        <v>1029</v>
+      </c>
+      <c r="L77" t="n">
+        <v>104</v>
+      </c>
+      <c r="M77" t="n">
+        <v>1.047</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:31.642</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>1780022610175</v>
+      </c>
+      <c r="C78" t="n">
+        <v>82848</v>
+      </c>
+      <c r="D78" t="n">
+        <v>253.6</v>
+      </c>
+      <c r="E78" t="n">
+        <v>92</v>
+      </c>
+      <c r="F78" t="n">
+        <v>1259</v>
+      </c>
+      <c r="G78" t="n">
+        <v>309.22</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J78" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K78" t="n">
+        <v>1466</v>
+      </c>
+      <c r="L78" t="n">
+        <v>123</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0.6860000000000001</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:31.644</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>1780022610375</v>
+      </c>
+      <c r="C79" t="n">
+        <v>83469</v>
+      </c>
+      <c r="D79" t="n">
+        <v>861.92</v>
+      </c>
+      <c r="E79" t="n">
+        <v>92</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1259</v>
+      </c>
+      <c r="G79" t="n">
+        <v>309.22</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J79" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K79" t="n">
+        <v>1268</v>
+      </c>
+      <c r="L79" t="n">
+        <v>111</v>
+      </c>
+      <c r="M79" t="n">
+        <v>1.053</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:31.646</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>1780022610575</v>
+      </c>
+      <c r="C80" t="n">
+        <v>83550</v>
+      </c>
+      <c r="D80" t="n">
+        <v>899.83</v>
+      </c>
+      <c r="E80" t="n">
+        <v>86</v>
+      </c>
+      <c r="F80" t="n">
+        <v>1279</v>
+      </c>
+      <c r="G80" t="n">
+        <v>326.35</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J80" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K80" t="n">
+        <v>1069</v>
+      </c>
+      <c r="L80" t="n">
+        <v>114</v>
+      </c>
+      <c r="M80" t="n">
+        <v>1.86</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:32.429</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>1780022610775</v>
+      </c>
+      <c r="C81" t="n">
+        <v>83518</v>
+      </c>
+      <c r="D81" t="n">
+        <v>822.83</v>
+      </c>
+      <c r="E81" t="n">
+        <v>86</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1279</v>
+      </c>
+      <c r="G81" t="n">
+        <v>326.35</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J81" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K81" t="n">
+        <v>1653</v>
+      </c>
+      <c r="L81" t="n">
+        <v>118</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0.669</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:32.430</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>1780022610975</v>
+      </c>
+      <c r="C82" t="n">
+        <v>83135</v>
+      </c>
+      <c r="D82" t="n">
+        <v>398.69</v>
+      </c>
+      <c r="E82" t="n">
+        <v>86</v>
+      </c>
+      <c r="F82" t="n">
+        <v>1279</v>
+      </c>
+      <c r="G82" t="n">
+        <v>326.35</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J82" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K82" t="n">
+        <v>1454</v>
+      </c>
+      <c r="L82" t="n">
+        <v>108</v>
+      </c>
+      <c r="M82" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:32.431</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>1780022611175</v>
+      </c>
+      <c r="C83" t="n">
+        <v>83154</v>
+      </c>
+      <c r="D83" t="n">
+        <v>397.76</v>
+      </c>
+      <c r="E83" t="n">
+        <v>86</v>
+      </c>
+      <c r="F83" t="n">
+        <v>1279</v>
+      </c>
+      <c r="G83" t="n">
+        <v>326.35</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J83" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K83" t="n">
+        <v>1255</v>
+      </c>
+      <c r="L83" t="n">
+        <v>119</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:32.433</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>1780022611375</v>
+      </c>
+      <c r="C84" t="n">
+        <v>83486</v>
+      </c>
+      <c r="D84" t="n">
+        <v>709.87</v>
+      </c>
+      <c r="E84" t="n">
+        <v>86</v>
+      </c>
+      <c r="F84" t="n">
+        <v>1279</v>
+      </c>
+      <c r="G84" t="n">
+        <v>326.35</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J84" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K84" t="n">
+        <v>1057</v>
+      </c>
+      <c r="L84" t="n">
+        <v>110</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0.967</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:32.995</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>1780022611575</v>
+      </c>
+      <c r="C85" t="n">
+        <v>82918</v>
+      </c>
+      <c r="D85" t="n">
+        <v>106.38</v>
+      </c>
+      <c r="E85" t="n">
+        <v>55</v>
+      </c>
+      <c r="F85" t="n">
+        <v>1080</v>
+      </c>
+      <c r="G85" t="n">
+        <v>302.57</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J85" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K85" t="n">
+        <v>1418</v>
+      </c>
+      <c r="L85" t="n">
+        <v>106</v>
+      </c>
+      <c r="M85" t="n">
+        <v>1.738</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:32.997</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>1780022611794</v>
+      </c>
+      <c r="C86" t="n">
+        <v>83015</v>
+      </c>
+      <c r="D86" t="n">
+        <v>198.06</v>
+      </c>
+      <c r="E86" t="n">
+        <v>55</v>
+      </c>
+      <c r="F86" t="n">
+        <v>1080</v>
+      </c>
+      <c r="G86" t="n">
+        <v>302.57</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J86" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K86" t="n">
+        <v>1202</v>
+      </c>
+      <c r="L86" t="n">
+        <v>116</v>
+      </c>
+      <c r="M86" t="n">
+        <v>1.347</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:33.459</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>1780022611994</v>
+      </c>
+      <c r="C87" t="n">
+        <v>83018</v>
+      </c>
+      <c r="D87" t="n">
+        <v>191.15</v>
+      </c>
+      <c r="E87" t="n">
+        <v>55</v>
+      </c>
+      <c r="F87" t="n">
+        <v>1080</v>
+      </c>
+      <c r="G87" t="n">
+        <v>302.57</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J87" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K87" t="n">
+        <v>1464</v>
+      </c>
+      <c r="L87" t="n">
+        <v>112</v>
+      </c>
+      <c r="M87" t="n">
+        <v>1.328</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:33.468</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>1780022612194</v>
+      </c>
+      <c r="C88" t="n">
+        <v>82802</v>
+      </c>
+      <c r="D88" t="n">
+        <v>-34.4</v>
+      </c>
+      <c r="E88" t="n">
+        <v>55</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1080</v>
+      </c>
+      <c r="G88" t="n">
+        <v>302.57</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J88" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K88" t="n">
+        <v>1273</v>
+      </c>
+      <c r="L88" t="n">
+        <v>121</v>
+      </c>
+      <c r="M88" t="n">
+        <v>1.762</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:33.470</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>1780022612394</v>
+      </c>
+      <c r="C89" t="n">
+        <v>83614</v>
+      </c>
+      <c r="D89" t="n">
+        <v>779.3200000000001</v>
+      </c>
+      <c r="E89" t="n">
+        <v>55</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1080</v>
+      </c>
+      <c r="G89" t="n">
+        <v>302.57</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J89" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K89" t="n">
+        <v>1075</v>
+      </c>
+      <c r="L89" t="n">
+        <v>103</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:33.472</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>1780022612594</v>
+      </c>
+      <c r="C90" t="n">
+        <v>83306</v>
+      </c>
+      <c r="D90" t="n">
+        <v>432.35</v>
+      </c>
+      <c r="E90" t="n">
+        <v>54</v>
+      </c>
+      <c r="F90" t="n">
+        <v>879</v>
+      </c>
+      <c r="G90" t="n">
+        <v>305.81</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J90" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K90" t="n">
+        <v>877</v>
+      </c>
+      <c r="L90" t="n">
+        <v>104</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0.725</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:34.030</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>1780022612794</v>
+      </c>
+      <c r="C91" t="n">
+        <v>83859</v>
+      </c>
+      <c r="D91" t="n">
+        <v>963.73</v>
+      </c>
+      <c r="E91" t="n">
+        <v>54</v>
+      </c>
+      <c r="F91" t="n">
+        <v>879</v>
+      </c>
+      <c r="G91" t="n">
+        <v>305.81</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J91" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K91" t="n">
+        <v>1234</v>
+      </c>
+      <c r="L91" t="n">
+        <v>115</v>
+      </c>
+      <c r="M91" t="n">
+        <v>1.502</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:34.047</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>1780022612994</v>
+      </c>
+      <c r="C92" t="n">
+        <v>83989</v>
+      </c>
+      <c r="D92" t="n">
+        <v>1045.55</v>
+      </c>
+      <c r="E92" t="n">
+        <v>54</v>
+      </c>
+      <c r="F92" t="n">
+        <v>879</v>
+      </c>
+      <c r="G92" t="n">
+        <v>305.81</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J92" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K92" t="n">
+        <v>1051</v>
+      </c>
+      <c r="L92" t="n">
+        <v>106</v>
+      </c>
+      <c r="M92" t="n">
+        <v>1.499</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:34.165</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>1780022613194</v>
+      </c>
+      <c r="C93" t="n">
+        <v>83331</v>
+      </c>
+      <c r="D93" t="n">
+        <v>335.27</v>
+      </c>
+      <c r="E93" t="n">
+        <v>54</v>
+      </c>
+      <c r="F93" t="n">
+        <v>879</v>
+      </c>
+      <c r="G93" t="n">
+        <v>305.81</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J93" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K93" t="n">
+        <v>970</v>
+      </c>
+      <c r="L93" t="n">
+        <v>110</v>
+      </c>
+      <c r="M93" t="n">
+        <v>1.066</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:34.167</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>1780022613394</v>
+      </c>
+      <c r="C94" t="n">
+        <v>83542</v>
+      </c>
+      <c r="D94" t="n">
+        <v>529.51</v>
+      </c>
+      <c r="E94" t="n">
+        <v>54</v>
+      </c>
+      <c r="F94" t="n">
+        <v>879</v>
+      </c>
+      <c r="G94" t="n">
+        <v>305.81</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J94" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K94" t="n">
+        <v>772</v>
+      </c>
+      <c r="L94" t="n">
+        <v>110</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0.973</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:34.806</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>1780022613613</v>
+      </c>
+      <c r="C95" t="n">
+        <v>83907</v>
+      </c>
+      <c r="D95" t="n">
+        <v>868.03</v>
+      </c>
+      <c r="E95" t="n">
+        <v>54</v>
+      </c>
+      <c r="F95" t="n">
+        <v>879</v>
+      </c>
+      <c r="G95" t="n">
+        <v>305.81</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J95" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K95" t="n">
+        <v>1192</v>
+      </c>
+      <c r="L95" t="n">
+        <v>111</v>
+      </c>
+      <c r="M95" t="n">
+        <v>1.045</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:34.833</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>1780022613813</v>
+      </c>
+      <c r="C96" t="n">
+        <v>83315</v>
+      </c>
+      <c r="D96" t="n">
+        <v>232.63</v>
+      </c>
+      <c r="E96" t="n">
+        <v>54</v>
+      </c>
+      <c r="F96" t="n">
+        <v>1199</v>
+      </c>
+      <c r="G96" t="n">
+        <v>311.94</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J96" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K96" t="n">
+        <v>1019</v>
+      </c>
+      <c r="L96" t="n">
+        <v>110</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0.522</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:35.170</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>1780022614013</v>
+      </c>
+      <c r="C97" t="n">
+        <v>83028</v>
+      </c>
+      <c r="D97" t="n">
+        <v>-66</v>
+      </c>
+      <c r="E97" t="n">
+        <v>54</v>
+      </c>
+      <c r="F97" t="n">
+        <v>1199</v>
+      </c>
+      <c r="G97" t="n">
+        <v>311.94</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I97" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J97" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K97" t="n">
+        <v>1155</v>
+      </c>
+      <c r="L97" t="n">
+        <v>125</v>
+      </c>
+      <c r="M97" t="n">
+        <v>1.691</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:35.177</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>1780022614213</v>
+      </c>
+      <c r="C98" t="n">
+        <v>83024</v>
+      </c>
+      <c r="D98" t="n">
+        <v>-66.7</v>
+      </c>
+      <c r="E98" t="n">
+        <v>54</v>
+      </c>
+      <c r="F98" t="n">
+        <v>1199</v>
+      </c>
+      <c r="G98" t="n">
+        <v>311.94</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J98" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K98" t="n">
+        <v>963</v>
+      </c>
+      <c r="L98" t="n">
+        <v>110</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0.592</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:35.903</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>1780022614413</v>
+      </c>
+      <c r="C99" t="n">
+        <v>83419</v>
+      </c>
+      <c r="D99" t="n">
+        <v>331.63</v>
+      </c>
+      <c r="E99" t="n">
+        <v>54</v>
+      </c>
+      <c r="F99" t="n">
+        <v>1199</v>
+      </c>
+      <c r="G99" t="n">
+        <v>311.94</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I99" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J99" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K99" t="n">
+        <v>1489</v>
+      </c>
+      <c r="L99" t="n">
+        <v>124</v>
+      </c>
+      <c r="M99" t="n">
+        <v>1.239</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:35.905</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>1780022614613</v>
+      </c>
+      <c r="C100" t="n">
+        <v>81478</v>
+      </c>
+      <c r="D100" t="n">
+        <v>-1625.95</v>
+      </c>
+      <c r="E100" t="n">
+        <v>60</v>
+      </c>
+      <c r="F100" t="n">
+        <v>880</v>
+      </c>
+      <c r="G100" t="n">
+        <v>300.93</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I100" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J100" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K100" t="n">
+        <v>1291</v>
+      </c>
+      <c r="L100" t="n">
+        <v>105</v>
+      </c>
+      <c r="M100" t="n">
+        <v>1.524</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:36.461</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>1780022614813</v>
+      </c>
+      <c r="C101" t="n">
+        <v>83422</v>
+      </c>
+      <c r="D101" t="n">
+        <v>399.35</v>
+      </c>
+      <c r="E101" t="n">
+        <v>60</v>
+      </c>
+      <c r="F101" t="n">
+        <v>880</v>
+      </c>
+      <c r="G101" t="n">
+        <v>300.93</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I101" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J101" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K101" t="n">
+        <v>1647</v>
+      </c>
+      <c r="L101" t="n">
+        <v>135</v>
+      </c>
+      <c r="M101" t="n">
+        <v>1.082</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:36.462</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>1780022615013</v>
+      </c>
+      <c r="C102" t="n">
+        <v>84741</v>
+      </c>
+      <c r="D102" t="n">
+        <v>1698.38</v>
+      </c>
+      <c r="E102" t="n">
+        <v>60</v>
+      </c>
+      <c r="F102" t="n">
+        <v>880</v>
+      </c>
+      <c r="G102" t="n">
+        <v>300.93</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J102" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K102" t="n">
+        <v>1449</v>
+      </c>
+      <c r="L102" t="n">
+        <v>106</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:36.463</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>1780022615232</v>
+      </c>
+      <c r="C103" t="n">
+        <v>84086</v>
+      </c>
+      <c r="D103" t="n">
+        <v>958.46</v>
+      </c>
+      <c r="E103" t="n">
+        <v>60</v>
+      </c>
+      <c r="F103" t="n">
+        <v>880</v>
+      </c>
+      <c r="G103" t="n">
+        <v>300.93</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I103" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J103" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K103" t="n">
+        <v>1231</v>
+      </c>
+      <c r="L103" t="n">
+        <v>108</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0.627</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:36.465</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>1780022615432</v>
+      </c>
+      <c r="C104" t="n">
+        <v>83420</v>
+      </c>
+      <c r="D104" t="n">
+        <v>244.54</v>
+      </c>
+      <c r="E104" t="n">
+        <v>60</v>
+      </c>
+      <c r="F104" t="n">
+        <v>880</v>
+      </c>
+      <c r="G104" t="n">
+        <v>300.93</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I104" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J104" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K104" t="n">
+        <v>1032</v>
+      </c>
+      <c r="L104" t="n">
+        <v>109</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0.968</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:36.886</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>1780022615632</v>
+      </c>
+      <c r="C105" t="n">
+        <v>82785</v>
+      </c>
+      <c r="D105" t="n">
+        <v>-402.69</v>
+      </c>
+      <c r="E105" t="n">
+        <v>60</v>
+      </c>
+      <c r="F105" t="n">
+        <v>880</v>
+      </c>
+      <c r="G105" t="n">
+        <v>300.93</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I105" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J105" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K105" t="n">
+        <v>1253</v>
+      </c>
+      <c r="L105" t="n">
+        <v>115</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0.983</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:36.916</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>1780022615832</v>
+      </c>
+      <c r="C106" t="n">
+        <v>82713</v>
+      </c>
+      <c r="D106" t="n">
+        <v>-454.55</v>
+      </c>
+      <c r="E106" t="n">
+        <v>60</v>
+      </c>
+      <c r="F106" t="n">
+        <v>880</v>
+      </c>
+      <c r="G106" t="n">
+        <v>300.93</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I106" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J106" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K106" t="n">
+        <v>1083</v>
+      </c>
+      <c r="L106" t="n">
+        <v>114</v>
+      </c>
+      <c r="M106" t="n">
+        <v>1.008</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:36.919</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>1780022616032</v>
+      </c>
+      <c r="C107" t="n">
+        <v>82991</v>
+      </c>
+      <c r="D107" t="n">
+        <v>-153.83</v>
+      </c>
+      <c r="E107" t="n">
+        <v>60</v>
+      </c>
+      <c r="F107" t="n">
+        <v>880</v>
+      </c>
+      <c r="G107" t="n">
+        <v>300.93</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I107" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J107" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K107" t="n">
+        <v>885</v>
+      </c>
+      <c r="L107" t="n">
+        <v>105</v>
+      </c>
+      <c r="M107" t="n">
+        <v>1.353</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:37.409</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>1780022616232</v>
+      </c>
+      <c r="C108" t="n">
+        <v>82827</v>
+      </c>
+      <c r="D108" t="n">
+        <v>-310.13</v>
+      </c>
+      <c r="E108" t="n">
+        <v>60</v>
+      </c>
+      <c r="F108" t="n">
+        <v>880</v>
+      </c>
+      <c r="G108" t="n">
+        <v>300.93</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I108" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J108" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K108" t="n">
+        <v>1177</v>
+      </c>
+      <c r="L108" t="n">
+        <v>108</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0.647</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:37.411</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>1780022616432</v>
+      </c>
+      <c r="C109" t="n">
+        <v>83156</v>
+      </c>
+      <c r="D109" t="n">
+        <v>34.37</v>
+      </c>
+      <c r="E109" t="n">
+        <v>60</v>
+      </c>
+      <c r="F109" t="n">
+        <v>880</v>
+      </c>
+      <c r="G109" t="n">
+        <v>300.93</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I109" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J109" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K109" t="n">
+        <v>977</v>
+      </c>
+      <c r="L109" t="n">
+        <v>116</v>
+      </c>
+      <c r="M109" t="n">
+        <v>1.248</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:38.025</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>1780022616632</v>
+      </c>
+      <c r="C110" t="n">
+        <v>83042</v>
+      </c>
+      <c r="D110" t="n">
+        <v>-81.34999999999999</v>
+      </c>
+      <c r="E110" t="n">
+        <v>60</v>
+      </c>
+      <c r="F110" t="n">
+        <v>880</v>
+      </c>
+      <c r="G110" t="n">
+        <v>300.93</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I110" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J110" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K110" t="n">
+        <v>1392</v>
+      </c>
+      <c r="L110" t="n">
+        <v>113</v>
+      </c>
+      <c r="M110" t="n">
+        <v>0.978</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:38.027</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>1780022616832</v>
+      </c>
+      <c r="C111" t="n">
+        <v>83027</v>
+      </c>
+      <c r="D111" t="n">
+        <v>-92.28</v>
+      </c>
+      <c r="E111" t="n">
+        <v>60</v>
+      </c>
+      <c r="F111" t="n">
+        <v>880</v>
+      </c>
+      <c r="G111" t="n">
+        <v>300.93</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I111" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J111" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K111" t="n">
+        <v>1194</v>
+      </c>
+      <c r="L111" t="n">
+        <v>105</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0.901</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:38.028</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>1780022617051</v>
+      </c>
+      <c r="C112" t="n">
+        <v>82942</v>
+      </c>
+      <c r="D112" t="n">
+        <v>-172.67</v>
+      </c>
+      <c r="E112" t="n">
+        <v>60</v>
+      </c>
+      <c r="F112" t="n">
+        <v>880</v>
+      </c>
+      <c r="G112" t="n">
+        <v>300.93</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I112" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J112" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K112" t="n">
+        <v>976</v>
+      </c>
+      <c r="L112" t="n">
+        <v>107</v>
+      </c>
+      <c r="M112" t="n">
+        <v>1.071</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:38.528</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>1780022617251</v>
+      </c>
+      <c r="C113" t="n">
+        <v>82871</v>
+      </c>
+      <c r="D113" t="n">
+        <v>-235.03</v>
+      </c>
+      <c r="E113" t="n">
+        <v>60</v>
+      </c>
+      <c r="F113" t="n">
+        <v>880</v>
+      </c>
+      <c r="G113" t="n">
+        <v>300.93</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I113" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J113" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K113" t="n">
+        <v>1276</v>
+      </c>
+      <c r="L113" t="n">
+        <v>115</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0.617</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:39.504</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>1780022617451</v>
+      </c>
+      <c r="C114" t="n">
+        <v>82865</v>
+      </c>
+      <c r="D114" t="n">
+        <v>-229.28</v>
+      </c>
+      <c r="E114" t="n">
+        <v>60</v>
+      </c>
+      <c r="F114" t="n">
+        <v>880</v>
+      </c>
+      <c r="G114" t="n">
+        <v>300.93</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I114" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J114" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K114" t="n">
+        <v>2052</v>
+      </c>
+      <c r="L114" t="n">
+        <v>112</v>
+      </c>
+      <c r="M114" t="n">
+        <v>1.022</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:39.516</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>1780022617651</v>
+      </c>
+      <c r="C115" t="n">
+        <v>82310</v>
+      </c>
+      <c r="D115" t="n">
+        <v>-772.8200000000001</v>
+      </c>
+      <c r="E115" t="n">
+        <v>60</v>
+      </c>
+      <c r="F115" t="n">
+        <v>880</v>
+      </c>
+      <c r="G115" t="n">
+        <v>300.93</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I115" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J115" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K115" t="n">
+        <v>1864</v>
+      </c>
+      <c r="L115" t="n">
+        <v>115</v>
+      </c>
+      <c r="M115" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:39.518</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>1780022617851</v>
+      </c>
+      <c r="C116" t="n">
+        <v>82293</v>
+      </c>
+      <c r="D116" t="n">
+        <v>-751.1799999999999</v>
+      </c>
+      <c r="E116" t="n">
+        <v>60</v>
+      </c>
+      <c r="F116" t="n">
+        <v>880</v>
+      </c>
+      <c r="G116" t="n">
+        <v>300.93</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I116" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J116" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K116" t="n">
+        <v>1666</v>
+      </c>
+      <c r="L116" t="n">
+        <v>107</v>
+      </c>
+      <c r="M116" t="n">
+        <v>0.901</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:39.519</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>1780022618051</v>
+      </c>
+      <c r="C117" t="n">
+        <v>82497</v>
+      </c>
+      <c r="D117" t="n">
+        <v>-509.62</v>
+      </c>
+      <c r="E117" t="n">
+        <v>60</v>
+      </c>
+      <c r="F117" t="n">
+        <v>880</v>
+      </c>
+      <c r="G117" t="n">
+        <v>300.93</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I117" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J117" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K117" t="n">
+        <v>1467</v>
+      </c>
+      <c r="L117" t="n">
+        <v>104</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.822</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:39.722</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>1780022618251</v>
+      </c>
+      <c r="C118" t="n">
+        <v>83325</v>
+      </c>
+      <c r="D118" t="n">
+        <v>343.86</v>
+      </c>
+      <c r="E118" t="n">
+        <v>60</v>
+      </c>
+      <c r="F118" t="n">
+        <v>880</v>
+      </c>
+      <c r="G118" t="n">
+        <v>300.93</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I118" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J118" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K118" t="n">
+        <v>1469</v>
+      </c>
+      <c r="L118" t="n">
+        <v>114</v>
+      </c>
+      <c r="M118" t="n">
+        <v>1.674</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:39.737</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>1780022618451</v>
+      </c>
+      <c r="C119" t="n">
+        <v>84169</v>
+      </c>
+      <c r="D119" t="n">
+        <v>1170.67</v>
+      </c>
+      <c r="E119" t="n">
+        <v>60</v>
+      </c>
+      <c r="F119" t="n">
+        <v>3758</v>
+      </c>
+      <c r="G119" t="n">
+        <v>300.93</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I119" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J119" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K119" t="n">
+        <v>1285</v>
+      </c>
+      <c r="L119" t="n">
+        <v>108</v>
+      </c>
+      <c r="M119" t="n">
+        <v>1.265</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:39.761</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>1780022618670</v>
+      </c>
+      <c r="C120" t="n">
+        <v>83536</v>
+      </c>
+      <c r="D120" t="n">
+        <v>479.14</v>
+      </c>
+      <c r="E120" t="n">
+        <v>60</v>
+      </c>
+      <c r="F120" t="n">
+        <v>3758</v>
+      </c>
+      <c r="G120" t="n">
+        <v>300.93</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I120" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J120" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1090</v>
+      </c>
+      <c r="L120" t="n">
+        <v>110</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.983</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:39.774</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>1780022618870</v>
+      </c>
+      <c r="C121" t="n">
+        <v>83612</v>
+      </c>
+      <c r="D121" t="n">
+        <v>531.1799999999999</v>
+      </c>
+      <c r="E121" t="n">
+        <v>60</v>
+      </c>
+      <c r="F121" t="n">
+        <v>3758</v>
+      </c>
+      <c r="G121" t="n">
+        <v>300.93</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J121" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K121" t="n">
+        <v>903</v>
+      </c>
+      <c r="L121" t="n">
+        <v>108</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.575</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:40.141</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>1780022619070</v>
+      </c>
+      <c r="C122" t="n">
+        <v>83754</v>
+      </c>
+      <c r="D122" t="n">
+        <v>646.62</v>
+      </c>
+      <c r="E122" t="n">
+        <v>60</v>
+      </c>
+      <c r="F122" t="n">
+        <v>3758</v>
+      </c>
+      <c r="G122" t="n">
+        <v>300.93</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
+        <v>49.44</v>
+      </c>
+      <c r="J122" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K122" t="n">
+        <v>1069</v>
+      </c>
+      <c r="L122" t="n">
+        <v>113</v>
+      </c>
+      <c r="M122" t="n">
+        <v>1.427</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:40.142</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>1780022619270</v>
+      </c>
+      <c r="C123" t="n">
+        <v>83526</v>
+      </c>
+      <c r="D123" t="n">
+        <v>386.29</v>
+      </c>
+      <c r="E123" t="n">
+        <v>60</v>
+      </c>
+      <c r="F123" t="n">
+        <v>3758</v>
+      </c>
+      <c r="G123" t="n">
+        <v>300.93</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I123" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J123" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K123" t="n">
+        <v>871</v>
+      </c>
+      <c r="L123" t="n">
+        <v>106</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.797</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:41.137</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>1780022619470</v>
+      </c>
+      <c r="C124" t="n">
+        <v>83539</v>
+      </c>
+      <c r="D124" t="n">
+        <v>379.98</v>
+      </c>
+      <c r="E124" t="n">
+        <v>60</v>
+      </c>
+      <c r="F124" t="n">
+        <v>3758</v>
+      </c>
+      <c r="G124" t="n">
+        <v>300.93</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I124" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="J124" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K124" t="n">
+        <v>1666</v>
+      </c>
+      <c r="L124" t="n">
+        <v>106</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.946</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:41.154</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>1780022619670</v>
+      </c>
+      <c r="C125" t="n">
+        <v>83666</v>
+      </c>
+      <c r="D125" t="n">
+        <v>487.98</v>
+      </c>
+      <c r="E125" t="n">
+        <v>60</v>
+      </c>
+      <c r="F125" t="n">
+        <v>3758</v>
+      </c>
+      <c r="G125" t="n">
+        <v>300.93</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I125" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J125" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K125" t="n">
+        <v>1483</v>
+      </c>
+      <c r="L125" t="n">
+        <v>107</v>
+      </c>
+      <c r="M125" t="n">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:41.507</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>1780022619870</v>
+      </c>
+      <c r="C126" t="n">
+        <v>84078</v>
+      </c>
+      <c r="D126" t="n">
+        <v>875.58</v>
+      </c>
+      <c r="E126" t="n">
+        <v>57</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1419</v>
+      </c>
+      <c r="G126" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I126" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J126" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K126" t="n">
+        <v>1635</v>
+      </c>
+      <c r="L126" t="n">
+        <v>117</v>
+      </c>
+      <c r="M126" t="n">
+        <v>1.266</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:41.508</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>1780022620070</v>
+      </c>
+      <c r="C127" t="n">
+        <v>84295</v>
+      </c>
+      <c r="D127" t="n">
+        <v>1048.8</v>
+      </c>
+      <c r="E127" t="n">
+        <v>57</v>
+      </c>
+      <c r="F127" t="n">
+        <v>1419</v>
+      </c>
+      <c r="G127" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I127" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J127" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K127" t="n">
+        <v>1437</v>
+      </c>
+      <c r="L127" t="n">
+        <v>117</v>
+      </c>
+      <c r="M127" t="n">
+        <v>1.249</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:41.509</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>1780022620289</v>
+      </c>
+      <c r="C128" t="n">
+        <v>82720</v>
+      </c>
+      <c r="D128" t="n">
+        <v>-578.64</v>
+      </c>
+      <c r="E128" t="n">
+        <v>57</v>
+      </c>
+      <c r="F128" t="n">
+        <v>1419</v>
+      </c>
+      <c r="G128" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I128" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J128" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K128" t="n">
+        <v>1219</v>
+      </c>
+      <c r="L128" t="n">
+        <v>106</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.549</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:41.510</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>1780022620489</v>
+      </c>
+      <c r="C129" t="n">
+        <v>83533</v>
+      </c>
+      <c r="D129" t="n">
+        <v>263.29</v>
+      </c>
+      <c r="E129" t="n">
+        <v>57</v>
+      </c>
+      <c r="F129" t="n">
+        <v>1419</v>
+      </c>
+      <c r="G129" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I129" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J129" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K129" t="n">
+        <v>1020</v>
+      </c>
+      <c r="L129" t="n">
+        <v>118</v>
+      </c>
+      <c r="M129" t="n">
+        <v>1.067</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:42.128</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>1780022620689</v>
+      </c>
+      <c r="C130" t="n">
+        <v>82774</v>
+      </c>
+      <c r="D130" t="n">
+        <v>-508.87</v>
+      </c>
+      <c r="E130" t="n">
+        <v>57</v>
+      </c>
+      <c r="F130" t="n">
+        <v>1419</v>
+      </c>
+      <c r="G130" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I130" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J130" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K130" t="n">
+        <v>1438</v>
+      </c>
+      <c r="L130" t="n">
+        <v>120</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.948</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:42.129</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>1780022620889</v>
+      </c>
+      <c r="C131" t="n">
+        <v>82698</v>
+      </c>
+      <c r="D131" t="n">
+        <v>-559.4299999999999</v>
+      </c>
+      <c r="E131" t="n">
+        <v>57</v>
+      </c>
+      <c r="F131" t="n">
+        <v>1419</v>
+      </c>
+      <c r="G131" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I131" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J131" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K131" t="n">
+        <v>1240</v>
+      </c>
+      <c r="L131" t="n">
+        <v>122</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.638</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:42.599</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>1780022621089</v>
+      </c>
+      <c r="C132" t="n">
+        <v>82709</v>
+      </c>
+      <c r="D132" t="n">
+        <v>-520.46</v>
+      </c>
+      <c r="E132" t="n">
+        <v>57</v>
+      </c>
+      <c r="F132" t="n">
+        <v>1419</v>
+      </c>
+      <c r="G132" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I132" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J132" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K132" t="n">
+        <v>1509</v>
+      </c>
+      <c r="L132" t="n">
+        <v>117</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.916</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:42.600</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>1780022621289</v>
+      </c>
+      <c r="C133" t="n">
+        <v>84417</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1213.56</v>
+      </c>
+      <c r="E133" t="n">
+        <v>57</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1419</v>
+      </c>
+      <c r="G133" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J133" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K133" t="n">
+        <v>1310</v>
+      </c>
+      <c r="L133" t="n">
+        <v>113</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.632</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:42.601</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>1780022621489</v>
+      </c>
+      <c r="C134" t="n">
+        <v>83428</v>
+      </c>
+      <c r="D134" t="n">
+        <v>163.89</v>
+      </c>
+      <c r="E134" t="n">
+        <v>57</v>
+      </c>
+      <c r="F134" t="n">
+        <v>1419</v>
+      </c>
+      <c r="G134" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I134" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J134" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K134" t="n">
+        <v>1111</v>
+      </c>
+      <c r="L134" t="n">
+        <v>122</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.661</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:42.978</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>1780022621690</v>
+      </c>
+      <c r="C135" t="n">
+        <v>82938</v>
+      </c>
+      <c r="D135" t="n">
+        <v>-334.31</v>
+      </c>
+      <c r="E135" t="n">
+        <v>57</v>
+      </c>
+      <c r="F135" t="n">
+        <v>1419</v>
+      </c>
+      <c r="G135" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I135" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="J135" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K135" t="n">
+        <v>1286</v>
+      </c>
+      <c r="L135" t="n">
+        <v>107</v>
+      </c>
+      <c r="M135" t="n">
+        <v>1.126</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:42.979</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>1780022621889</v>
+      </c>
+      <c r="C136" t="n">
+        <v>82554</v>
+      </c>
+      <c r="D136" t="n">
+        <v>-701.59</v>
+      </c>
+      <c r="E136" t="n">
+        <v>57</v>
+      </c>
+      <c r="F136" t="n">
+        <v>1419</v>
+      </c>
+      <c r="G136" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I136" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J136" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K136" t="n">
+        <v>1089</v>
+      </c>
+      <c r="L136" t="n">
+        <v>120</v>
+      </c>
+      <c r="M136" t="n">
+        <v>1.036</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:43.292</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>1780022622108</v>
+      </c>
+      <c r="C137" t="n">
+        <v>82583</v>
+      </c>
+      <c r="D137" t="n">
+        <v>-637.51</v>
+      </c>
+      <c r="E137" t="n">
+        <v>57</v>
+      </c>
+      <c r="F137" t="n">
+        <v>1419</v>
+      </c>
+      <c r="G137" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I137" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J137" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K137" t="n">
+        <v>1182</v>
+      </c>
+      <c r="L137" t="n">
+        <v>127</v>
+      </c>
+      <c r="M137" t="n">
+        <v>1.536</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:43.318</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>1780022622308</v>
+      </c>
+      <c r="C138" t="n">
+        <v>83152</v>
+      </c>
+      <c r="D138" t="n">
+        <v>-36.64</v>
+      </c>
+      <c r="E138" t="n">
+        <v>57</v>
+      </c>
+      <c r="F138" t="n">
+        <v>1419</v>
+      </c>
+      <c r="G138" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I138" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J138" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K138" t="n">
+        <v>1008</v>
+      </c>
+      <c r="L138" t="n">
+        <v>120</v>
+      </c>
+      <c r="M138" t="n">
+        <v>1.167</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:44.285</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>1780022622509</v>
+      </c>
+      <c r="C139" t="n">
+        <v>83126</v>
+      </c>
+      <c r="D139" t="n">
+        <v>-60.81</v>
+      </c>
+      <c r="E139" t="n">
+        <v>57</v>
+      </c>
+      <c r="F139" t="n">
+        <v>1419</v>
+      </c>
+      <c r="G139" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I139" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="J139" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K139" t="n">
+        <v>1775</v>
+      </c>
+      <c r="L139" t="n">
+        <v>107</v>
+      </c>
+      <c r="M139" t="n">
+        <v>1.101</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:44.287</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>1780022622708</v>
+      </c>
+      <c r="C140" t="n">
+        <v>82298</v>
+      </c>
+      <c r="D140" t="n">
+        <v>-885.76</v>
+      </c>
+      <c r="E140" t="n">
+        <v>57</v>
+      </c>
+      <c r="F140" t="n">
+        <v>1419</v>
+      </c>
+      <c r="G140" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I140" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J140" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K140" t="n">
+        <v>1578</v>
+      </c>
+      <c r="L140" t="n">
+        <v>121</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.998</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:44.720</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>1780022622909</v>
+      </c>
+      <c r="C141" t="n">
+        <v>81293</v>
+      </c>
+      <c r="D141" t="n">
+        <v>-1846.48</v>
+      </c>
+      <c r="E141" t="n">
+        <v>57</v>
+      </c>
+      <c r="F141" t="n">
+        <v>1419</v>
+      </c>
+      <c r="G141" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I141" t="n">
+        <v>49.49</v>
+      </c>
+      <c r="J141" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K141" t="n">
+        <v>1810</v>
+      </c>
+      <c r="L141" t="n">
+        <v>106</v>
+      </c>
+      <c r="M141" t="n">
+        <v>1.141</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:44.732</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>1780022623108</v>
+      </c>
+      <c r="C142" t="n">
+        <v>82785</v>
+      </c>
+      <c r="D142" t="n">
+        <v>-262.15</v>
+      </c>
+      <c r="E142" t="n">
+        <v>57</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1419</v>
+      </c>
+      <c r="G142" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I142" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J142" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K142" t="n">
+        <v>1623</v>
+      </c>
+      <c r="L142" t="n">
+        <v>108</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.8159999999999999</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:44.733</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>1780022623308</v>
+      </c>
+      <c r="C143" t="n">
+        <v>81059</v>
+      </c>
+      <c r="D143" t="n">
+        <v>-1975.05</v>
+      </c>
+      <c r="E143" t="n">
+        <v>57</v>
+      </c>
+      <c r="F143" t="n">
+        <v>1419</v>
+      </c>
+      <c r="G143" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I143" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J143" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K143" t="n">
+        <v>1424</v>
+      </c>
+      <c r="L143" t="n">
+        <v>107</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.767</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:44.735</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>1780022623509</v>
+      </c>
+      <c r="C144" t="n">
+        <v>80049</v>
+      </c>
+      <c r="D144" t="n">
+        <v>-2886.29</v>
+      </c>
+      <c r="E144" t="n">
+        <v>57</v>
+      </c>
+      <c r="F144" t="n">
+        <v>1419</v>
+      </c>
+      <c r="G144" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I144" t="n">
+        <v>49.66</v>
+      </c>
+      <c r="J144" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K144" t="n">
+        <v>1224</v>
+      </c>
+      <c r="L144" t="n">
+        <v>106</v>
+      </c>
+      <c r="M144" t="n">
+        <v>0.991</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:44.936</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>1780022623727</v>
+      </c>
+      <c r="C145" t="n">
+        <v>80570</v>
+      </c>
+      <c r="D145" t="n">
+        <v>-2220.98</v>
+      </c>
+      <c r="E145" t="n">
+        <v>57</v>
+      </c>
+      <c r="F145" t="n">
+        <v>1419</v>
+      </c>
+      <c r="G145" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I145" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J145" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K145" t="n">
+        <v>1209</v>
+      </c>
+      <c r="L145" t="n">
+        <v>120</v>
+      </c>
+      <c r="M145" t="n">
+        <v>0.571</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:44.937</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>1780022623927</v>
+      </c>
+      <c r="C146" t="n">
+        <v>80942</v>
+      </c>
+      <c r="D146" t="n">
+        <v>-1737.93</v>
+      </c>
+      <c r="E146" t="n">
+        <v>57</v>
+      </c>
+      <c r="F146" t="n">
+        <v>1419</v>
+      </c>
+      <c r="G146" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I146" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J146" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K146" t="n">
+        <v>1010</v>
+      </c>
+      <c r="L146" t="n">
+        <v>121</v>
+      </c>
+      <c r="M146" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:45.283</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>1780022624128</v>
+      </c>
+      <c r="C147" t="n">
+        <v>81120</v>
+      </c>
+      <c r="D147" t="n">
+        <v>-1473.03</v>
+      </c>
+      <c r="E147" t="n">
+        <v>57</v>
+      </c>
+      <c r="F147" t="n">
+        <v>1419</v>
+      </c>
+      <c r="G147" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I147" t="n">
+        <v>49.55</v>
+      </c>
+      <c r="J147" t="n">
+        <v>36.27</v>
+      </c>
+      <c r="K147" t="n">
+        <v>1154</v>
+      </c>
+      <c r="L147" t="n">
+        <v>156</v>
+      </c>
+      <c r="M147" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:45.284</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>1780022624328</v>
+      </c>
+      <c r="C148" t="n">
+        <v>81456</v>
+      </c>
+      <c r="D148" t="n">
+        <v>-1063.38</v>
+      </c>
+      <c r="E148" t="n">
+        <v>57</v>
+      </c>
+      <c r="F148" t="n">
+        <v>1419</v>
+      </c>
+      <c r="G148" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I148" t="n">
+        <v>49.48</v>
+      </c>
+      <c r="J148" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K148" t="n">
+        <v>955</v>
+      </c>
+      <c r="L148" t="n">
+        <v>110</v>
+      </c>
+      <c r="M148" t="n">
+        <v>0.877</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:45.286</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>1780022624527</v>
+      </c>
+      <c r="C149" t="n">
+        <v>81534</v>
+      </c>
+      <c r="D149" t="n">
+        <v>-932.21</v>
+      </c>
+      <c r="E149" t="n">
+        <v>57</v>
+      </c>
+      <c r="F149" t="n">
+        <v>1419</v>
+      </c>
+      <c r="G149" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I149" t="n">
+        <v>49.44</v>
+      </c>
+      <c r="J149" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K149" t="n">
+        <v>758</v>
+      </c>
+      <c r="L149" t="n">
+        <v>111</v>
+      </c>
+      <c r="M149" t="n">
+        <v>0.881</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:45.838</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>1780022624727</v>
+      </c>
+      <c r="C150" t="n">
+        <v>81474</v>
+      </c>
+      <c r="D150" t="n">
+        <v>-945.6</v>
+      </c>
+      <c r="E150" t="n">
+        <v>57</v>
+      </c>
+      <c r="F150" t="n">
+        <v>1419</v>
+      </c>
+      <c r="G150" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I150" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J150" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K150" t="n">
+        <v>1110</v>
+      </c>
+      <c r="L150" t="n">
+        <v>116</v>
+      </c>
+      <c r="M150" t="n">
+        <v>1.043</v>
       </c>
     </row>
   </sheetData>
